--- a/Templates~/Config/Excels/L10n/LocalizedImages.xlsx
+++ b/Templates~/Config/Excels/L10n/LocalizedImages.xlsx
@@ -1,201 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Workspace\Unity\Game Dev Tools\Config\Excels\L10n\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{181BEAAE-D909-44FB-B9BF-76A98DB97953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4980" yWindow="4980" windowWidth="28815" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="4980" yWindow="4980" windowWidth="28815" windowHeight="15345" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Lx34r</author>
-  </authors>
-  <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{ADA07E4C-32F4-49F0-8BA5-688763A7DFDF}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Lx34r:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-游戏中使用：{l10n:key}/{i18n:key}/{g11n:key}</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C5" authorId="0" shapeId="0" xr:uid="{5D2B064A-BC4B-4CDE-8D3C-C4C1D237C0FB}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>Lx34r:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-必须与 __beans__.xlsx 中定义的 L10n.LocalizedImageBean 结构一致。
-顺序无所谓，根据第三行的标识来识别对应语言。</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>占位符</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>key</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>c</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>##var</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>zh-Hans</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>en</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>支持的多语言</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>res</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>L10n.LocalizationBean</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="2"/>
+      <color rgb="FF9C5700"/>
       <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color indexed="81"/>
       <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
-      <b/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color indexed="81"/>
       <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -206,7 +68,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -255,48 +117,152 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="适中" xfId="1" builtinId="28"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Lx34r</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0">
+      <text>
+        <t>Lx34r:
+游戏中使用：{l10n:key}/{i18n:key}/{g11n:key}</t>
+      </text>
+    </comment>
+    <comment ref="C5" authorId="0" shapeId="0">
+      <text>
+        <t>Lx34r:
+必须与 __beans__.xlsx 中定义的 L10n.LocalizedImageBean 结构一致。
+顺序无所谓，根据第三行的标识来识别对应语言。</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -548,83 +514,114 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="43.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5" customWidth="1"/>
-    <col min="4" max="4" width="26.75" customWidth="1"/>
+    <col width="43.875" bestFit="1" customWidth="1" style="6" min="2" max="2"/>
+    <col width="24.5" customWidth="1" style="6" min="3" max="3"/>
+    <col width="26.75" customWidth="1" style="6" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="D1" s="5"/>
+    <row r="1" customFormat="1" s="2">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>res</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="n"/>
     </row>
-    <row r="2" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="5"/>
+    <row r="2" customFormat="1" s="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>L10n.LocalizationBean</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="n"/>
     </row>
-    <row r="3" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="1"/>
-      <c r="C3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>10</v>
+    <row r="3" customFormat="1" s="2">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n"/>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>text@zh-Hans</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>text@en</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1"/>
-      <c r="C4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4" s="5"/>
+    <row r="4" customFormat="1" s="2">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>##group</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n"/>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n"/>
     </row>
-    <row r="5" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D5" s="5"/>
+    <row r="5" customFormat="1" s="2">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>占位符</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>支持的多语言</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="C2:D2"/>
+    <mergeCell ref="C5:D5"/>
     <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
   </mergeCells>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>